--- a/artfynd/A 43417-2023 artfynd.xlsx
+++ b/artfynd/A 43417-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43417-2023 artfynd.xlsx
+++ b/artfynd/A 43417-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112691444</v>
+        <v>112691447</v>
       </c>
       <c r="B2" t="n">
-        <v>78939</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557405</v>
+        <v>557561</v>
       </c>
       <c r="R2" t="n">
-        <v>7064145</v>
+        <v>7064143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112691445</v>
+        <v>112691442</v>
       </c>
       <c r="B3" t="n">
-        <v>78939</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557442</v>
+        <v>557540</v>
       </c>
       <c r="R3" t="n">
-        <v>7064143</v>
+        <v>7064166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,53 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112691448</v>
+        <v>112691500</v>
       </c>
       <c r="B4" t="n">
-        <v>78873</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Korpberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557573</v>
+        <v>557482</v>
       </c>
       <c r="R4" t="n">
-        <v>7064126</v>
+        <v>7064077</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,24 +956,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1012,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112691503</v>
+        <v>112691501</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557408</v>
+        <v>557473</v>
       </c>
       <c r="R5" t="n">
-        <v>7064100</v>
+        <v>7064075</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,50 +1079,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112691443</v>
+        <v>112691450</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Korpberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557405</v>
+        <v>557715</v>
       </c>
       <c r="R6" t="n">
-        <v>7064143</v>
+        <v>7064119</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,8 +1161,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1224,15 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112691446</v>
+        <v>112691451</v>
       </c>
       <c r="B7" t="n">
-        <v>78939</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557545</v>
+        <v>557731</v>
       </c>
       <c r="R7" t="n">
-        <v>7064154</v>
+        <v>7064129</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,37 +1300,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112691439</v>
+        <v>112691524</v>
       </c>
       <c r="B8" t="n">
-        <v>78966</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557452</v>
+        <v>557455</v>
       </c>
       <c r="R8" t="n">
-        <v>7064164</v>
+        <v>7064074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,16 +1404,11 @@
         <v>112691441</v>
       </c>
       <c r="B9" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1545,16 +1505,11 @@
         <v>112691525</v>
       </c>
       <c r="B10" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1582,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557419</v>
+        <v>557418</v>
       </c>
       <c r="R10" t="n">
-        <v>7064113</v>
+        <v>7064114</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,53 +1603,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112691526</v>
+        <v>112691448</v>
       </c>
       <c r="B11" t="n">
-        <v>55852</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Korpbeget, Ång</t>
+          <t>Korpberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557385</v>
+        <v>557572</v>
       </c>
       <c r="R11" t="n">
-        <v>7064143</v>
+        <v>7064127</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,8 +1685,24 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1757,12 +1726,7 @@
         <v>112691438</v>
       </c>
       <c r="B12" t="n">
-        <v>78939</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,15 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112691504</v>
+        <v>112691444</v>
       </c>
       <c r="B13" t="n">
-        <v>78939</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557410</v>
+        <v>557405</v>
       </c>
       <c r="R13" t="n">
-        <v>7064098</v>
+        <v>7064145</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,37 +1925,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112691442</v>
+        <v>112691445</v>
       </c>
       <c r="B14" t="n">
-        <v>90356</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2006,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557540</v>
+        <v>557442</v>
       </c>
       <c r="R14" t="n">
-        <v>7064166</v>
+        <v>7064143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,15 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112691447</v>
+        <v>112691446</v>
       </c>
       <c r="B15" t="n">
-        <v>86092</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2112,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557561</v>
+        <v>557545</v>
       </c>
       <c r="R15" t="n">
-        <v>7064143</v>
+        <v>7064154</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,15 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112691467</v>
+        <v>112691449</v>
       </c>
       <c r="B16" t="n">
-        <v>78939</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,16 +2156,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Korpberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557585</v>
+        <v>557715</v>
       </c>
       <c r="R16" t="n">
-        <v>7064124</v>
+        <v>7064119</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,22 +2209,23 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2299,15 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112691465</v>
+        <v>112691467</v>
       </c>
       <c r="B17" t="n">
-        <v>77629</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,21 +2258,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2339,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557562</v>
+        <v>557586</v>
       </c>
       <c r="R17" t="n">
-        <v>7064167</v>
+        <v>7064125</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,6 +2329,21 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
@@ -2398,6 +2356,930 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>112691468</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Korpberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>557721</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7064131</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund, Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112691502</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Korpberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>557449</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7064074</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund, Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>112691504</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Korpberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>557410</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7064098</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund, Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>112691439</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Korpberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>557452</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7064164</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund, Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>112691443</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Korpberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>557405</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7064143</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund, Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>112691503</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Korpberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>557408</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7064101</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund, Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>112691469</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Korpbeget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>557723</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7064139</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund, Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>112691526</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Korpbeget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>557385</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7064143</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund, Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>112691465</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Korpberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>557562</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7064167</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund, Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 43417-2023 artfynd.xlsx
+++ b/artfynd/A 43417-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691447</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691442</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691500</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691501</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691524</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691441</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,6 +1412,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691525</t>
         </is>
       </c>
     </row>
@@ -1499,6 +1539,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691448</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691438</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691444</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,6 +1857,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691445</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1903,6 +1963,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691446</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2019,6 +2084,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691467</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691502</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2221,6 +2296,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691504</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2322,6 +2402,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691439</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2423,6 +2508,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691443</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2524,6 +2614,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691503</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2625,6 +2720,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691526</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2724,6 +2824,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691465</t>
         </is>
       </c>
     </row>
@@ -2846,6 +2951,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691450</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2945,6 +3055,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691451</t>
         </is>
       </c>
     </row>
@@ -3067,6 +3182,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691449</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3183,6 +3303,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691468</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3284,8 +3409,40 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691469</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>